--- a/data/trans_orig/IP39-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP39-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31395</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>33709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106166</t>
+          <t>106300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103337</t>
+          <t>105692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>129914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194309</t>
+          <t>193664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229910</t>
+          <t>227769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>54375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>51345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73958</t>
+          <t>73103</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>101255</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3374,47 +3374,47 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5806</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5741</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -3565,82 +3565,82 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5625</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>602</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>40078</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>57344</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>88032</t>
+          <t>88686</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>111839</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29388</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>53276</t>
+          <t>52669</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75248</t>
+          <t>75226</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>54997</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28857</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>37837</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>44500</t>
+          <t>44040</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>43693</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>55527</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>80903</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>24169</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>43750</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>137856</t>
+          <t>139322</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>168254</t>
+          <t>168149</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>159774</t>
+          <t>159120</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>193304</t>
+          <t>192145</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>306530</t>
+          <t>308378</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>349259</t>
+          <t>349577</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>39037</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>63039</t>
+          <t>61286</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>50498</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>75009</t>
+          <t>76161</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>104153</t>
+          <t>105479</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>62123</t>
+          <t>62027</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>86731</t>
+          <t>87035</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>59043</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>84613</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>127977</t>
+          <t>128493</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>164683</t>
+          <t>162109</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33592</t>
+          <t>33562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40426</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37111</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49069</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73851</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7537,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -7876,12 +7876,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60064</t>
+          <t>58955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82443</t>
+          <t>81564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69929</t>
+          <t>71509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92474</t>
+          <t>94420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136040</t>
+          <t>136434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168476</t>
+          <t>170697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -8102,12 +8102,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8117,12 +8117,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8137,12 +8137,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8215,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>27381</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45640</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>56913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82633</t>
+          <t>80906</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -8671,12 +8671,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -8784,12 +8784,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8897,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9236,12 +9236,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>40692</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>57020</t>
+          <t>57635</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56320</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>85786</t>
+          <t>85337</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>109990</t>
+          <t>109328</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>56979</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>22447</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49129</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>42807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9918,12 +9918,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>30862</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>50737</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46911</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9968,12 +9968,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62570</t>
+          <t>62848</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>89029</t>
+          <t>89840</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -10031,12 +10031,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -10144,12 +10144,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -10257,12 +10257,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -10370,12 +10370,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>110180</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>140135</t>
+          <t>139416</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>126269</t>
+          <t>123191</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>157728</t>
+          <t>154364</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>244082</t>
+          <t>246146</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>286671</t>
+          <t>286696</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>43916</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>43222</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>80570</t>
+          <t>80297</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>48440</t>
+          <t>48052</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>71739</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>48752</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>71907</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>103569</t>
+          <t>102673</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>136718</t>
+          <t>137104</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11298,12 +11298,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11431,12 +11431,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -11848,12 +11848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11883,12 +11883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -11961,12 +11961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -12643,12 +12643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12713,12 +12713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>30148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12826,12 +12826,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -12869,12 +12869,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12884,12 +12884,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12919,12 +12919,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12939,12 +12939,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -12982,12 +12982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12997,12 +12997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>29332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13032,12 +13032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13052,12 +13052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>30102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51666</t>
+          <t>50660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13067,12 +13067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -13165,12 +13165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96078</t>
+          <t>96047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>73928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96980</t>
+          <t>96565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13278,12 +13278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153951</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186596</t>
+          <t>185209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13391,12 +13391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13406,12 +13406,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -13434,12 +13434,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30319</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>48544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13504,12 +13504,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63322</t>
+          <t>64364</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88896</t>
+          <t>90853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13925,12 +13925,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13940,12 +13940,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13960,12 +13960,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13975,12 +13975,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -14003,12 +14003,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14038,12 +14038,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14073,12 +14073,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -14116,12 +14116,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14186,12 +14186,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14201,12 +14201,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -14229,12 +14229,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14299,12 +14299,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14314,12 +14314,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -14342,12 +14342,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14412,12 +14412,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14427,12 +14427,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -14455,12 +14455,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14525,12 +14525,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>101022</t>
+          <t>100666</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>126652</t>
+          <t>125640</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14540,12 +14540,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -14568,12 +14568,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14603,12 +14603,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14618,12 +14618,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14638,12 +14638,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>40441</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>61516</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14653,12 +14653,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -14681,12 +14681,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14716,12 +14716,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14731,12 +14731,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14751,12 +14751,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22046</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39064</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -14911,12 +14911,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14981,12 +14981,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -15024,12 +15024,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15059,12 +15059,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15094,12 +15094,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15109,12 +15109,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -15137,12 +15137,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>24319</t>
+          <t>24492</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>43104</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15187,12 +15187,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15207,12 +15207,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>46996</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15222,12 +15222,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -15250,12 +15250,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15285,12 +15285,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15320,12 +15320,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>30895</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15335,12 +15335,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -15363,12 +15363,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21049</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15398,12 +15398,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15413,12 +15413,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15433,12 +15433,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>31425</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15448,12 +15448,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -15476,12 +15476,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33847</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15491,12 +15491,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>39636</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15526,12 +15526,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -15589,12 +15589,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15604,12 +15604,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>59633</t>
+          <t>61722</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -15702,12 +15702,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>124689</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>154569</t>
+          <t>154341</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15717,12 +15717,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>136167</t>
+          <t>138014</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>166410</t>
+          <t>169326</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15752,12 +15752,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>271374</t>
+          <t>271018</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>311463</t>
+          <t>314607</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -15815,12 +15815,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>40579</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15830,12 +15830,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>56514</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>81479</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -15928,12 +15928,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44231</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>65618</t>
+          <t>65903</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15943,12 +15943,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15963,12 +15963,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>45344</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>68130</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>94670</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>126501</t>
+          <t>127228</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
